--- a/Excel/MonsterBabelConfig.xlsx
+++ b/Excel/MonsterBabelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -146,6 +146,24 @@
   </si>
   <si>
     <t>64E+10</t>
+  </si>
+  <si>
+    <t>4E+12</t>
+  </si>
+  <si>
+    <t>8E+11</t>
+  </si>
+  <si>
+    <t>68E+17</t>
+  </si>
+  <si>
+    <t>1.0163</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>71E+24</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1139,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AA13"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.58333333333333" style="1" customWidth="1"/>
@@ -1151,7 +1169,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1"/>
     <row r="2" s="1" customFormat="1" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +1246,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="C4" s="4" t="s">
         <v>25</v>
       </c>
@@ -1305,7 +1323,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="C5" s="4" t="s">
         <v>26</v>
       </c>
@@ -1382,7 +1400,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:27">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:27">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1459,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:27">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:27">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1541,23 +1559,102 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:27">
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:27">
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <f>F7+1</f>
+        <v>2001</v>
+      </c>
+      <c r="F8" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>Q7+(F7-E7+1)*R7</f>
+        <v>40</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="S8" s="2">
+        <f>S7+(F7-E7+1)*T7</f>
+        <v>160</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="U8" s="2">
+        <f>U7+(F7-E7+1)*V7</f>
+        <v>40</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="W8" s="2">
+        <f>W7+(F7-E7+1)*X7</f>
+        <v>40</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>50</v>
+      </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:27">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:27">
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
+      <c r="K9" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:27">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:27">
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -1565,7 +1662,7 @@
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:27">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:27">
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -1573,7 +1670,7 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:27">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:27">
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -1581,7 +1678,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:27">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:27">
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>

--- a/Excel/MonsterBabelConfig.xlsx
+++ b/Excel/MonsterBabelConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
   <si>
     <t>ID</t>
   </si>
@@ -154,6 +154,9 @@
     <t>8E+11</t>
   </si>
   <si>
+    <t>1.0186</t>
+  </si>
+  <si>
     <t>68E+17</t>
   </si>
   <si>
@@ -161,6 +164,12 @@
   </si>
   <si>
     <t>#</t>
+  </si>
+  <si>
+    <t>4E+17</t>
+  </si>
+  <si>
+    <t>8E+19</t>
   </si>
   <si>
     <t>71E+24</t>
@@ -1485,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2">
-        <f>F6+1</f>
+        <f t="shared" ref="E7:E9" si="0">F6+1</f>
         <v>1001</v>
       </c>
       <c r="F7" s="2">
@@ -1510,10 +1519,10 @@
         <v>33</v>
       </c>
       <c r="M7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O7" s="2">
         <v>0</v>
@@ -1522,28 +1531,28 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2">
-        <f>Q6+(F6-E6+1)*R6</f>
+        <f t="shared" ref="Q7:Q9" si="1">Q6+(F6-E6+1)*R6</f>
         <v>20</v>
       </c>
       <c r="R7" s="2">
         <v>0.02</v>
       </c>
       <c r="S7" s="2">
-        <f>S6+(F6-E6+1)*T6</f>
+        <f t="shared" ref="S7:S9" si="2">S6+(F6-E6+1)*T6</f>
         <v>100</v>
       </c>
       <c r="T7" s="2">
         <v>0.06</v>
       </c>
       <c r="U7" s="2">
-        <f>U6+(F6-E6+1)*V6</f>
+        <f t="shared" ref="U7:U9" si="3">U6+(F6-E6+1)*V6</f>
         <v>20</v>
       </c>
       <c r="V7" s="2">
         <v>0.02</v>
       </c>
       <c r="W7" s="2">
-        <f>W6+(F6-E6+1)*X6</f>
+        <f t="shared" ref="W7:W9" si="4">W6+(F6-E6+1)*X6</f>
         <v>20</v>
       </c>
       <c r="X7" s="2">
@@ -1567,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <f>F7+1</f>
+        <f t="shared" si="0"/>
         <v>2001</v>
       </c>
       <c r="F8" s="2">
@@ -1583,49 +1592,51 @@
         <v>38</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M8" s="2">
-        <v>1</v>
+        <f>M7+(F7-E7+1)*N7</f>
+        <v>500</v>
       </c>
       <c r="N8" s="2">
         <v>1</v>
       </c>
       <c r="O8" s="2">
+        <f>O7+(F7-E7+1)*P7</f>
         <v>0</v>
       </c>
       <c r="P8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2">
-        <f>Q7+(F7-E7+1)*R7</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="R8" s="2">
         <v>0.02</v>
       </c>
       <c r="S8" s="2">
-        <f>S7+(F7-E7+1)*T7</f>
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="T8" s="2">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="U8" s="2">
-        <f>U7+(F7-E7+1)*V7</f>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="V8" s="2">
         <v>0.02</v>
       </c>
       <c r="W8" s="2">
-        <f>W7+(F7-E7+1)*X7</f>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="X8" s="2">
@@ -1643,16 +1654,90 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:27">
       <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
+        <v>3001</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4000</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" s="5"/>
+      <c r="M9" s="2">
+        <f>M8+(F8-E8+1)*N8</f>
+        <v>1500</v>
+      </c>
+      <c r="N9" s="2">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2">
+        <f>O8+(F8-E8+1)*P8</f>
+        <v>1000</v>
+      </c>
+      <c r="P9" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="S9" s="2">
+        <f t="shared" si="2"/>
+        <v>300</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="U9" s="2">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="W9" s="2">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:27">
       <c r="G10" s="5"/>
